--- a/artfynd/A 16996-2025 artfynd.xlsx
+++ b/artfynd/A 16996-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1356,6 +1356,450 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>124782871</v>
+      </c>
+      <c r="B8" t="n">
+        <v>105117</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>A 16996, Hålbäcken, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>574764</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6443552</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ukna</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>124782791</v>
+      </c>
+      <c r="B9" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>A 16996, Hålbäcken, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>574719</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6443548</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ukna</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>124783112</v>
+      </c>
+      <c r="B10" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>A 16996, Hålbäcken, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>574758</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6443544</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ukna</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>124782830</v>
+      </c>
+      <c r="B11" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>A 16996, Hålbäcken, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>574749</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6443515</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ukna</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 16996-2025 artfynd.xlsx
+++ b/artfynd/A 16996-2025 artfynd.xlsx
@@ -1358,10 +1358,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124782871</v>
+        <v>124782791</v>
       </c>
       <c r="B8" t="n">
-        <v>105117</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1370,25 +1370,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1406,10 +1406,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>574764</v>
+        <v>574719</v>
       </c>
       <c r="R8" t="n">
-        <v>6443552</v>
+        <v>6443548</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1469,7 +1469,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124782791</v>
+        <v>124782830</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1517,10 +1517,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>574719</v>
+        <v>574749</v>
       </c>
       <c r="R9" t="n">
-        <v>6443548</v>
+        <v>6443515</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1580,10 +1580,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124783112</v>
+        <v>124782871</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
+        <v>105117</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1592,25 +1592,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1628,10 +1628,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>574758</v>
+        <v>574764</v>
       </c>
       <c r="R10" t="n">
-        <v>6443544</v>
+        <v>6443552</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1691,7 +1691,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124782830</v>
+        <v>124783112</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1739,10 +1739,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>574749</v>
+        <v>574758</v>
       </c>
       <c r="R11" t="n">
-        <v>6443515</v>
+        <v>6443544</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 16996-2025 artfynd.xlsx
+++ b/artfynd/A 16996-2025 artfynd.xlsx
@@ -1358,10 +1358,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124782791</v>
+        <v>124782871</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>105117</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1370,25 +1370,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1406,10 +1406,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>574719</v>
+        <v>574764</v>
       </c>
       <c r="R8" t="n">
-        <v>6443548</v>
+        <v>6443552</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1469,7 +1469,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124782830</v>
+        <v>124782791</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1517,10 +1517,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>574749</v>
+        <v>574719</v>
       </c>
       <c r="R9" t="n">
-        <v>6443515</v>
+        <v>6443548</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1580,10 +1580,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124782871</v>
+        <v>124782830</v>
       </c>
       <c r="B10" t="n">
-        <v>105117</v>
+        <v>98101</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1592,25 +1592,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1628,10 +1628,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>574764</v>
+        <v>574749</v>
       </c>
       <c r="R10" t="n">
-        <v>6443552</v>
+        <v>6443515</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 16996-2025 artfynd.xlsx
+++ b/artfynd/A 16996-2025 artfynd.xlsx
@@ -1358,10 +1358,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124782871</v>
+        <v>124782830</v>
       </c>
       <c r="B8" t="n">
-        <v>105117</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1370,25 +1370,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1406,10 +1406,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>574764</v>
+        <v>574749</v>
       </c>
       <c r="R8" t="n">
-        <v>6443552</v>
+        <v>6443515</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1469,10 +1469,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124782791</v>
+        <v>124782871</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
+        <v>105117</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1481,25 +1481,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1517,10 +1517,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>574719</v>
+        <v>574764</v>
       </c>
       <c r="R9" t="n">
-        <v>6443548</v>
+        <v>6443552</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1580,7 +1580,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124782830</v>
+        <v>124782791</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1628,10 +1628,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>574749</v>
+        <v>574719</v>
       </c>
       <c r="R10" t="n">
-        <v>6443515</v>
+        <v>6443548</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 16996-2025 artfynd.xlsx
+++ b/artfynd/A 16996-2025 artfynd.xlsx
@@ -1358,7 +1358,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124782830</v>
+        <v>124782791</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1406,10 +1406,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>574749</v>
+        <v>574719</v>
       </c>
       <c r="R8" t="n">
-        <v>6443515</v>
+        <v>6443548</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1580,7 +1580,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124782791</v>
+        <v>124783112</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1628,10 +1628,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>574719</v>
+        <v>574758</v>
       </c>
       <c r="R10" t="n">
-        <v>6443548</v>
+        <v>6443544</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1691,7 +1691,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124783112</v>
+        <v>124782830</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1739,10 +1739,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>574758</v>
+        <v>574749</v>
       </c>
       <c r="R11" t="n">
-        <v>6443544</v>
+        <v>6443515</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 16996-2025 artfynd.xlsx
+++ b/artfynd/A 16996-2025 artfynd.xlsx
@@ -1469,10 +1469,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124782871</v>
+        <v>124782830</v>
       </c>
       <c r="B9" t="n">
-        <v>105117</v>
+        <v>98101</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1481,25 +1481,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1517,10 +1517,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>574764</v>
+        <v>574749</v>
       </c>
       <c r="R9" t="n">
-        <v>6443552</v>
+        <v>6443515</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1580,10 +1580,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124783112</v>
+        <v>124782871</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
+        <v>105117</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1592,25 +1592,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1628,10 +1628,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>574758</v>
+        <v>574764</v>
       </c>
       <c r="R10" t="n">
-        <v>6443544</v>
+        <v>6443552</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1691,7 +1691,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124782830</v>
+        <v>124783112</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1739,10 +1739,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>574749</v>
+        <v>574758</v>
       </c>
       <c r="R11" t="n">
-        <v>6443515</v>
+        <v>6443544</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 16996-2025 artfynd.xlsx
+++ b/artfynd/A 16996-2025 artfynd.xlsx
@@ -1358,7 +1358,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124782791</v>
+        <v>124782830</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1406,10 +1406,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>574719</v>
+        <v>574749</v>
       </c>
       <c r="R8" t="n">
-        <v>6443548</v>
+        <v>6443515</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1469,7 +1469,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124782830</v>
+        <v>124782791</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1517,10 +1517,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>574749</v>
+        <v>574719</v>
       </c>
       <c r="R9" t="n">
-        <v>6443515</v>
+        <v>6443548</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 16996-2025 artfynd.xlsx
+++ b/artfynd/A 16996-2025 artfynd.xlsx
@@ -1358,7 +1358,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124782830</v>
+        <v>124783112</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1406,10 +1406,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>574749</v>
+        <v>574758</v>
       </c>
       <c r="R8" t="n">
-        <v>6443515</v>
+        <v>6443544</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1580,10 +1580,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124782871</v>
+        <v>124782830</v>
       </c>
       <c r="B10" t="n">
-        <v>105117</v>
+        <v>98101</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1592,25 +1592,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1628,10 +1628,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>574764</v>
+        <v>574749</v>
       </c>
       <c r="R10" t="n">
-        <v>6443552</v>
+        <v>6443515</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1691,10 +1691,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124783112</v>
+        <v>124782871</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>105117</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1703,25 +1703,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1739,10 +1739,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>574758</v>
+        <v>574764</v>
       </c>
       <c r="R11" t="n">
-        <v>6443544</v>
+        <v>6443552</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 16996-2025 artfynd.xlsx
+++ b/artfynd/A 16996-2025 artfynd.xlsx
@@ -1358,7 +1358,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124783112</v>
+        <v>124782791</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1406,10 +1406,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>574758</v>
+        <v>574719</v>
       </c>
       <c r="R8" t="n">
-        <v>6443544</v>
+        <v>6443548</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1469,7 +1469,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124782791</v>
+        <v>124782830</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1517,10 +1517,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>574719</v>
+        <v>574749</v>
       </c>
       <c r="R9" t="n">
-        <v>6443548</v>
+        <v>6443515</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1580,7 +1580,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124782830</v>
+        <v>124783112</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1628,10 +1628,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>574749</v>
+        <v>574758</v>
       </c>
       <c r="R10" t="n">
-        <v>6443515</v>
+        <v>6443544</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 16996-2025 artfynd.xlsx
+++ b/artfynd/A 16996-2025 artfynd.xlsx
@@ -1358,7 +1358,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124782791</v>
+        <v>124783112</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1406,10 +1406,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>574719</v>
+        <v>574758</v>
       </c>
       <c r="R8" t="n">
-        <v>6443548</v>
+        <v>6443544</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1469,10 +1469,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124782830</v>
+        <v>124782871</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
+        <v>105117</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1481,25 +1481,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1517,10 +1517,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>574749</v>
+        <v>574764</v>
       </c>
       <c r="R9" t="n">
-        <v>6443515</v>
+        <v>6443552</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1580,7 +1580,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124783112</v>
+        <v>124782791</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1628,10 +1628,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>574758</v>
+        <v>574719</v>
       </c>
       <c r="R10" t="n">
-        <v>6443544</v>
+        <v>6443548</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1691,10 +1691,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124782871</v>
+        <v>124782830</v>
       </c>
       <c r="B11" t="n">
-        <v>105117</v>
+        <v>98101</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1703,25 +1703,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1739,10 +1739,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>574764</v>
+        <v>574749</v>
       </c>
       <c r="R11" t="n">
-        <v>6443552</v>
+        <v>6443515</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 16996-2025 artfynd.xlsx
+++ b/artfynd/A 16996-2025 artfynd.xlsx
@@ -1462,17 +1462,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124782871</v>
+        <v>124782830</v>
       </c>
       <c r="B9" t="n">
-        <v>105117</v>
+        <v>98101</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1481,25 +1481,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1517,10 +1517,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>574764</v>
+        <v>574749</v>
       </c>
       <c r="R9" t="n">
-        <v>6443552</v>
+        <v>6443515</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1580,10 +1580,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124782791</v>
+        <v>124782871</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
+        <v>105117</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1592,25 +1592,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1628,10 +1628,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>574719</v>
+        <v>574764</v>
       </c>
       <c r="R10" t="n">
-        <v>6443548</v>
+        <v>6443552</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1691,7 +1691,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124782830</v>
+        <v>124782791</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1739,10 +1739,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>574749</v>
+        <v>574719</v>
       </c>
       <c r="R11" t="n">
-        <v>6443515</v>
+        <v>6443548</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 16996-2025 artfynd.xlsx
+++ b/artfynd/A 16996-2025 artfynd.xlsx
@@ -1358,7 +1358,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124783112</v>
+        <v>124782830</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1406,10 +1406,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>574758</v>
+        <v>574749</v>
       </c>
       <c r="R8" t="n">
-        <v>6443544</v>
+        <v>6443515</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1462,14 +1462,14 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124782830</v>
+        <v>124783112</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1517,10 +1517,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>574749</v>
+        <v>574758</v>
       </c>
       <c r="R9" t="n">
-        <v>6443515</v>
+        <v>6443544</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1580,10 +1580,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124782871</v>
+        <v>124782791</v>
       </c>
       <c r="B10" t="n">
-        <v>105117</v>
+        <v>98101</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1592,25 +1592,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1628,10 +1628,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>574764</v>
+        <v>574719</v>
       </c>
       <c r="R10" t="n">
-        <v>6443552</v>
+        <v>6443548</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1691,10 +1691,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124782791</v>
+        <v>124782871</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>105117</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1703,25 +1703,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1739,10 +1739,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>574719</v>
+        <v>574764</v>
       </c>
       <c r="R11" t="n">
-        <v>6443548</v>
+        <v>6443552</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 16996-2025 artfynd.xlsx
+++ b/artfynd/A 16996-2025 artfynd.xlsx
@@ -1358,7 +1358,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124782830</v>
+        <v>124783112</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1406,10 +1406,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>574749</v>
+        <v>574758</v>
       </c>
       <c r="R8" t="n">
-        <v>6443515</v>
+        <v>6443544</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1469,10 +1469,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124783112</v>
+        <v>124782871</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
+        <v>105117</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1481,25 +1481,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1517,10 +1517,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>574758</v>
+        <v>574764</v>
       </c>
       <c r="R9" t="n">
-        <v>6443544</v>
+        <v>6443552</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1691,10 +1691,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124782871</v>
+        <v>124782830</v>
       </c>
       <c r="B11" t="n">
-        <v>105117</v>
+        <v>98101</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1703,25 +1703,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1739,10 +1739,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>574764</v>
+        <v>574749</v>
       </c>
       <c r="R11" t="n">
-        <v>6443552</v>
+        <v>6443515</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 16996-2025 artfynd.xlsx
+++ b/artfynd/A 16996-2025 artfynd.xlsx
@@ -1358,7 +1358,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124783112</v>
+        <v>124782830</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1406,10 +1406,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>574758</v>
+        <v>574749</v>
       </c>
       <c r="R8" t="n">
-        <v>6443544</v>
+        <v>6443515</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1469,10 +1469,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124782871</v>
+        <v>124783112</v>
       </c>
       <c r="B9" t="n">
-        <v>105117</v>
+        <v>98101</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1481,25 +1481,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1517,10 +1517,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>574764</v>
+        <v>574758</v>
       </c>
       <c r="R9" t="n">
-        <v>6443552</v>
+        <v>6443544</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1691,10 +1691,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124782830</v>
+        <v>124782871</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>105117</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1703,25 +1703,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1739,10 +1739,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>574749</v>
+        <v>574764</v>
       </c>
       <c r="R11" t="n">
-        <v>6443515</v>
+        <v>6443552</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 16996-2025 artfynd.xlsx
+++ b/artfynd/A 16996-2025 artfynd.xlsx
@@ -1462,7 +1462,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1580,10 +1580,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124782791</v>
+        <v>124782871</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
+        <v>105117</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1592,25 +1592,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1628,10 +1628,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>574719</v>
+        <v>574764</v>
       </c>
       <c r="R10" t="n">
-        <v>6443548</v>
+        <v>6443552</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1684,17 +1684,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124782871</v>
+        <v>124782791</v>
       </c>
       <c r="B11" t="n">
-        <v>105117</v>
+        <v>98101</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1703,25 +1703,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1739,10 +1739,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>574764</v>
+        <v>574719</v>
       </c>
       <c r="R11" t="n">
-        <v>6443552</v>
+        <v>6443548</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 16996-2025 artfynd.xlsx
+++ b/artfynd/A 16996-2025 artfynd.xlsx
@@ -1361,7 +1361,7 @@
         <v>124782830</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1462,17 +1462,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124783112</v>
+        <v>124782791</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1517,10 +1517,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>574758</v>
+        <v>574719</v>
       </c>
       <c r="R9" t="n">
-        <v>6443544</v>
+        <v>6443548</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1583,7 +1583,7 @@
         <v>124782871</v>
       </c>
       <c r="B10" t="n">
-        <v>105117</v>
+        <v>105293</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1684,17 +1684,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124782791</v>
+        <v>124783112</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1739,10 +1739,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>574719</v>
+        <v>574758</v>
       </c>
       <c r="R11" t="n">
-        <v>6443548</v>
+        <v>6443544</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 16996-2025 artfynd.xlsx
+++ b/artfynd/A 16996-2025 artfynd.xlsx
@@ -1469,7 +1469,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124782791</v>
+        <v>124783112</v>
       </c>
       <c r="B9" t="n">
         <v>98269</v>
@@ -1517,10 +1517,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>574719</v>
+        <v>574758</v>
       </c>
       <c r="R9" t="n">
-        <v>6443548</v>
+        <v>6443544</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1691,7 +1691,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124783112</v>
+        <v>124782791</v>
       </c>
       <c r="B11" t="n">
         <v>98269</v>
@@ -1739,10 +1739,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>574758</v>
+        <v>574719</v>
       </c>
       <c r="R11" t="n">
-        <v>6443544</v>
+        <v>6443548</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 16996-2025 artfynd.xlsx
+++ b/artfynd/A 16996-2025 artfynd.xlsx
@@ -1108,7 +1108,7 @@
         <v>0</v>
       </c>
       <c r="AE5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">

--- a/artfynd/A 16996-2025 artfynd.xlsx
+++ b/artfynd/A 16996-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>99410496</v>
+        <v>99410475</v>
       </c>
       <c r="B2" t="n">
-        <v>93132</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2671</v>
+        <v>210</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>574714.5458519396</v>
+        <v>574725</v>
       </c>
       <c r="R2" t="n">
-        <v>6443536.345244145</v>
+        <v>6443450</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,21 +743,11 @@
           <t>2022-02-11</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-02-14</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -771,6 +756,11 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>granved</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -787,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>99410466</v>
+        <v>99410476</v>
       </c>
       <c r="B3" t="n">
-        <v>92939</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2779</v>
+        <v>210</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>574810.5624996877</v>
+        <v>574766</v>
       </c>
       <c r="R3" t="n">
-        <v>6443524.417598149</v>
+        <v>6443493</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -860,21 +845,11 @@
           <t>2022-02-11</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-02-14</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -883,6 +858,11 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>granved</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -899,15 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>99410476</v>
+        <v>99410477</v>
       </c>
       <c r="B4" t="n">
-        <v>93235</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -939,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>574765.6403448711</v>
+        <v>574877</v>
       </c>
       <c r="R4" t="n">
-        <v>6443492.933567003</v>
+        <v>6443431</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -972,19 +947,9 @@
           <t>2022-02-11</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-02-14</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1019,12 +984,7 @@
         <v>99410400</v>
       </c>
       <c r="B5" t="n">
-        <v>95246</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97811</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1056,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>574805.4708215111</v>
+        <v>574806</v>
       </c>
       <c r="R5" t="n">
-        <v>6443513.756773718</v>
+        <v>6443514</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1089,19 +1049,9 @@
           <t>2022-02-11</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-02-14</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1129,15 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>99410477</v>
+        <v>99410403</v>
       </c>
       <c r="B6" t="n">
-        <v>93235</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96437</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1145,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>210</v>
+        <v>2667</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1169,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>574876.3491741316</v>
+        <v>574703</v>
       </c>
       <c r="R6" t="n">
-        <v>6443431.627712254</v>
+        <v>6443555</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1202,21 +1147,11 @@
           <t>2022-02-11</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-02-14</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1225,11 +1160,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>granved</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1246,15 +1176,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>99410510</v>
+        <v>99410496</v>
       </c>
       <c r="B7" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1262,21 +1187,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>2671</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1286,10 +1211,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>574833.6896895521</v>
+        <v>574714</v>
       </c>
       <c r="R7" t="n">
-        <v>6443504.779685783</v>
+        <v>6443537</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1319,19 +1244,9 @@
           <t>2022-02-11</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-02-14</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1358,61 +1273,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124782830</v>
+        <v>99410466</v>
       </c>
       <c r="B8" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96231</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>2779</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>A 16996, Hålbäcken, Sm</t>
+          <t>Skjåsjön, Stjälkhammar, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>574749</v>
+        <v>574810</v>
       </c>
       <c r="R8" t="n">
-        <v>6443515</v>
+        <v>6443525</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1436,12 +1338,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-05-05</t>
+          <t>2022-02-11</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-05-05</t>
+          <t>2022-02-14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1450,77 +1352,74 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124783112</v>
+        <v>89345132</v>
       </c>
       <c r="B9" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>A 16996, Hålbäcken, Sm</t>
+          <t>Kalkbarrskog Skjåsjön, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>574758</v>
+        <v>574879</v>
       </c>
       <c r="R9" t="n">
-        <v>6443544</v>
+        <v>6443463</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1547,12 +1446,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-05-05</t>
+          <t>2020-10-03</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-05-05</t>
+          <t>2020-10-03</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1568,59 +1467,61 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Tobias Ivarsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
+          <t>Tobias Ivarsson, Jenny Ivarsson, Hugo Ivarsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124782871</v>
+        <v>124782905</v>
       </c>
       <c r="B10" t="n">
-        <v>105293</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221144</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1628,10 +1529,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>574764</v>
+        <v>574876</v>
       </c>
       <c r="R10" t="n">
-        <v>6443552</v>
+        <v>6443456</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1691,58 +1592,56 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124782791</v>
+        <v>89345133</v>
       </c>
       <c r="B11" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92567</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6031</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>A 16996, Hålbäcken, Sm</t>
+          <t>Kalkbarrskog Skjåsjön, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>574719</v>
+        <v>574858</v>
       </c>
       <c r="R11" t="n">
-        <v>6443548</v>
+        <v>6443466</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1769,12 +1668,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-05-05</t>
+          <t>2020-10-03</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-05-05</t>
+          <t>2020-10-03</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1790,15 +1689,1163 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson, Jenny Ivarsson, Hugo Ivarsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>99410353</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Skjåsjön, Stjälkhammar, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>574747</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6443569</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ukna</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2022-02-11</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2022-02-14</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>tallved</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>99410429</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Skjåsjön, Stjälkhammar, Sm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>574709</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6443544</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ukna</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2022-02-11</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2022-02-14</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>124782791</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>A 16996, Hålbäcken, Sm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>574719</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6443548</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ukna</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
           <t>Magnus Kasselstrand</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
+      <c r="AX14" t="inlineStr">
         <is>
           <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
-      <c r="AY11" t="inlineStr"/>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>124782830</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>A 16996, Hålbäcken, Sm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>574749</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6443515</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ukna</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>124783043</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>A 16996, Hålbäcken, Sm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>574744</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6443560</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ukna</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>124783079</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>A 16996, Hålbäcken, Sm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>574760</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6443557</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Ukna</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>124783112</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>A 16996, Hålbäcken, Sm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>574758</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6443544</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Ukna</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>124782871</v>
+      </c>
+      <c r="B19" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>A 16996, Hålbäcken, Sm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>574764</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6443552</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Ukna</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>89345141</v>
+      </c>
+      <c r="B20" t="n">
+        <v>102225</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>221223</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Vippärt</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lathyrus niger</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog Skjåsjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>574794</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6443550</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Ukna</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2020-10-03</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2020-10-03</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson, Jenny Ivarsson, Hugo Ivarsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>89345140</v>
+      </c>
+      <c r="B21" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog Skjåsjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>574794</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6443550</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Ukna</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2020-10-03</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2020-10-03</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson, Jenny Ivarsson, Hugo Ivarsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>99410510</v>
+      </c>
+      <c r="B22" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Skjåsjön, Stjälkhammar, Sm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>574833</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6443505</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Ukna</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2022-02-11</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2022-02-14</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
